--- a/originales/respuestas/2025/01. Calificadas/root/Unidad Administrativa Especial Cuerpo Oficial De Bomberos De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Unidad Administrativa Especial Cuerpo Oficial De Bomberos De Bogotá.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="173">
   <si>
     <t>Entidad</t>
   </si>
@@ -418,7 +418,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -427,13 +427,16 @@
     <t>Creación de equipos o laboratorios de innovación internos.</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
   </si>
   <si>
     <t>Convocatorias abiertas para proponer soluciones innovadoras.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Pregunta 32.</t>
@@ -5663,7 +5666,7 @@
       <c r="C16" s="7">
         <v>17.0</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="8" t="s">
         <v>128</v>
       </c>
       <c r="E16" s="6"/>
@@ -5706,7 +5709,7 @@
       <c r="C17" s="12">
         <v>18.0</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="13" t="s">
         <v>131</v>
       </c>
       <c r="E17" s="11"/>
@@ -5733,9 +5736,11 @@
         <v>1.0</v>
       </c>
       <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="13">
+      <c r="Q17" s="13">
         <v>1.0</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="S17" s="22"/>
       <c r="T17" s="27">
@@ -5753,16 +5758,16 @@
         <v>19.0</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>89</v>
@@ -6871,16 +6876,16 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>89</v>
@@ -6916,20 +6921,20 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>40</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J3" s="28"/>
       <c r="K3" s="25">
@@ -6961,20 +6966,20 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="23">
@@ -8096,16 +8101,16 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>89</v>
@@ -8141,20 +8146,20 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F3" s="28"/>
       <c r="G3" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>40</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J3" s="28"/>
       <c r="K3" s="25">
@@ -8186,20 +8191,20 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H4" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="23">
@@ -8231,22 +8236,22 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H5" s="22" t="s">
         <v>40</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J5" s="22"/>
       <c r="K5" s="23">
@@ -8278,20 +8283,20 @@
         <v>4.0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F6" s="28"/>
       <c r="G6" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H6" s="28" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J6" s="28"/>
       <c r="K6" s="25">
@@ -8323,22 +8328,22 @@
         <v>5.0</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H7" s="22" t="s">
         <v>40</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J7" s="22"/>
       <c r="K7" s="23">
@@ -8370,20 +8375,20 @@
         <v>5.0</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F8" s="22"/>
       <c r="G8" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J8" s="22"/>
       <c r="K8" s="23">
@@ -8415,22 +8420,22 @@
         <v>6.0</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H9" s="28" t="s">
         <v>40</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J9" s="28"/>
       <c r="K9" s="25">
@@ -8462,20 +8467,20 @@
         <v>7.0</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H10" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="23">
@@ -8509,16 +8514,16 @@
         <v>8.0</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H11" s="22" t="s">
         <v>89</v>
